--- a/Sample/chronogramme.xlsx
+++ b/Sample/chronogramme.xlsx
@@ -1,26 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julien.mousqueton@cohesity.com/Code/Murail/Sample/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://francis21.sharepoint.com/sites/DSI/Shared Documents/General/Teams - Cybersécurité/Murail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8225D56B-6909-A045-AF7B-B4C75364CD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="581" documentId="13_ncr:1_{8225D56B-6909-A045-AF7B-B4C75364CD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B925C49-FC54-47F0-A1AF-7537C758E4F5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$D$1:$D$276</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="279">
   <si>
     <t>id</t>
   </si>
@@ -2361,10 +2377,16 @@
 Le retex à chaud doit idéalement être complété par un retex à froid, qui permettra une analyse plus approfondie et objective une fois le recul nécessaire pris.</t>
   </si>
   <si>
-    <t>Publicité</t>
-  </si>
-  <si>
     <t>decompte</t>
+  </si>
+  <si>
+    <t>Frankie, expert en hautes technologies, fondateur de la master class "Défense - Horizons 2050"</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Pause du midi / Cyber</t>
   </si>
 </sst>
 </file>
@@ -2944,19 +2966,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I198"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J276"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="28"/>
-    <col min="4" max="4" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="28"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="71" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="43.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -2985,7 +3008,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="180" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="179.4" x14ac:dyDescent="0.3">
       <c r="A2" s="26">
         <v>1</v>
       </c>
@@ -3012,147 +3035,123 @@
       </c>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A3" s="26">
-        <v>2</v>
-      </c>
+    <row r="3" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="27"/>
       <c r="B3" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="12"/>
+    </row>
+    <row r="4" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.40138888888888885</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C4" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="12"/>
-    </row>
-    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A4" s="26">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.40277777777777773</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A5" s="27">
-        <v>4</v>
-      </c>
-      <c r="B5" s="13">
-        <v>0.40416666666666662</v>
+    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="27"/>
+      <c r="B5" s="4">
+        <v>0.4</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>29</v>
+        <v>275</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A6" s="27">
-        <v>5</v>
-      </c>
-      <c r="B6" s="13">
-        <v>0.4055555555555555</v>
-      </c>
-      <c r="C6" s="24" t="s">
+    <row r="6" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A6" s="26">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.40278935185185183</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="27">
-        <v>6</v>
-      </c>
-      <c r="B7" s="13">
-        <v>0.4069444444444445</v>
+    <row r="7" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="4">
+        <v>0.40347222222222223</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>33</v>
+        <v>275</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="I7" s="12"/>
     </row>
-    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A8" s="27">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" s="13">
-        <v>0.40833333333333338</v>
+        <v>0.40417824074074077</v>
       </c>
       <c r="C8" s="24" t="s">
         <v>9</v>
@@ -3160,163 +3159,137 @@
       <c r="D8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>34</v>
+      <c r="E8" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I8" s="12"/>
     </row>
-    <row r="9" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A9" s="27">
-        <v>8</v>
-      </c>
-      <c r="B9" s="13">
-        <v>0.41111111111111115</v>
+    <row r="9" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="27"/>
+      <c r="B9" s="4">
+        <v>0.40486111111111112</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>41</v>
+        <v>275</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A10" s="27">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" s="13">
-        <v>0.41388888888888892</v>
+        <v>0.40556712962962965</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A11" s="27">
+    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="27"/>
+      <c r="B11" s="4">
+        <v>0.40625</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A12" s="27">
+        <v>6</v>
+      </c>
+      <c r="B12" s="13">
+        <v>0.40695601851851854</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="165" x14ac:dyDescent="0.2">
-      <c r="A12" s="27">
-        <v>11</v>
-      </c>
-      <c r="B12" s="13">
-        <v>0.41944444444444401</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>49</v>
-      </c>
       <c r="E12" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="I12" s="12"/>
     </row>
-    <row r="13" spans="1:9" ht="180" x14ac:dyDescent="0.2">
-      <c r="A13" s="27">
-        <v>12</v>
-      </c>
-      <c r="B13" s="13">
-        <v>0.422222222222222</v>
+    <row r="13" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="27"/>
+      <c r="B13" s="4">
+        <v>0.40763888888888888</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>55</v>
+        <v>275</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6">
+        <v>1</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A14" s="27">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B14" s="13">
-        <v>0.42499999999999999</v>
+        <v>0.40834490740740742</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>9</v>
@@ -3325,326 +3298,276 @@
         <v>24</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A15" s="27">
-        <v>14</v>
-      </c>
-      <c r="B15" s="13">
-        <v>0.42777777777777798</v>
+    <row r="15" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="27"/>
+      <c r="B15" s="4">
+        <v>0.41041666666666665</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6">
+        <v>1</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="1:9" ht="69" x14ac:dyDescent="0.3">
+      <c r="A16" s="27">
+        <v>8</v>
+      </c>
+      <c r="B16" s="13">
+        <v>0.41112268518518519</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="12"/>
+    </row>
+    <row r="17" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="27"/>
+      <c r="B17" s="4">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6">
+        <v>1</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="12"/>
+    </row>
+    <row r="18" spans="1:10" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="27">
+        <v>9</v>
+      </c>
+      <c r="B18" s="13">
+        <v>0.41390046296296296</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="12"/>
+    </row>
+    <row r="19" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="27"/>
+      <c r="B19" s="4">
+        <v>0.4152777777777778</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="6">
+        <v>1</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="12"/>
+    </row>
+    <row r="20" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="27">
+        <v>10</v>
+      </c>
+      <c r="B20" s="13">
+        <v>0.41667824074074072</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="27"/>
+      <c r="B21" s="4">
+        <v>0.41875000000000001</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6">
+        <v>1</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="12"/>
+    </row>
+    <row r="22" spans="1:10" ht="193.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="27">
+        <v>11</v>
+      </c>
+      <c r="B22" s="13">
+        <v>0.41945601851851849</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E22" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="27"/>
+      <c r="B23" s="4">
+        <v>0.42152777777777778</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D23" s="9"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A16" s="27">
-        <v>15</v>
-      </c>
-      <c r="B16" s="13">
-        <v>0.43055555555555602</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="9" t="s">
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" spans="1:10" ht="165.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="27">
+        <v>12</v>
+      </c>
+      <c r="B24" s="13">
+        <v>0.42223379629629632</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="27"/>
+      <c r="B25" s="4">
+        <v>0.42430555555555555</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6">
+        <v>1</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="I16" s="12"/>
-    </row>
-    <row r="17" spans="1:9" ht="105" x14ac:dyDescent="0.2">
-      <c r="A17" s="27">
-        <v>16</v>
-      </c>
-      <c r="B17" s="13">
-        <v>0.43333333333333302</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I17" s="12"/>
-    </row>
-    <row r="18" spans="1:9" ht="135" x14ac:dyDescent="0.2">
-      <c r="A18" s="27">
-        <v>17</v>
-      </c>
-      <c r="B18" s="13">
-        <v>0.43611111111111101</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="I18" s="12"/>
-    </row>
-    <row r="19" spans="1:9" ht="150" x14ac:dyDescent="0.2">
-      <c r="A19" s="27">
-        <v>18</v>
-      </c>
-      <c r="B19" s="13">
-        <v>0.4375</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="135" x14ac:dyDescent="0.2">
-      <c r="A20" s="27">
-        <v>19</v>
-      </c>
-      <c r="B20" s="13">
-        <v>0.44027777777777777</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I20" s="12"/>
-    </row>
-    <row r="21" spans="1:9" ht="120" x14ac:dyDescent="0.2">
-      <c r="A21" s="27">
-        <v>20</v>
-      </c>
-      <c r="B21" s="13">
-        <v>0.44305555555555598</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="12"/>
-    </row>
-    <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A22" s="27">
-        <v>21</v>
-      </c>
-      <c r="B22" s="13">
-        <v>0.44583333333333303</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="I22" s="12"/>
-    </row>
-    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A23" s="27">
-        <v>22</v>
-      </c>
-      <c r="B23" s="13">
-        <v>0.44861111111111102</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="I23" s="12"/>
-    </row>
-    <row r="24" spans="1:9" ht="135" x14ac:dyDescent="0.2">
-      <c r="A24" s="27">
-        <v>23</v>
-      </c>
-      <c r="B24" s="13">
-        <v>0.45138888888888901</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="I24" s="12"/>
-    </row>
-    <row r="25" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A25" s="27">
-        <v>24</v>
-      </c>
-      <c r="B25" s="13">
-        <v>0.454166666666667</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>97</v>
-      </c>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="150" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="69" x14ac:dyDescent="0.3">
       <c r="A26" s="27">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B26" s="13">
-        <v>0.45694444444444399</v>
+        <v>0.42501157407407408</v>
       </c>
       <c r="C26" s="24" t="s">
         <v>9</v>
@@ -3653,54 +3576,44 @@
         <v>24</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="285" x14ac:dyDescent="0.2">
-      <c r="A27" s="27">
-        <v>26</v>
-      </c>
-      <c r="B27" s="13">
-        <v>0.45833333333333331</v>
+    <row r="27" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="27"/>
+      <c r="B27" s="4">
+        <v>0.42708333333333331</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="90" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6">
+        <v>1</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="12"/>
+    </row>
+    <row r="28" spans="1:10" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A28" s="27">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B28" s="13">
-        <v>0.46111111111111108</v>
+        <v>0.42778935185185185</v>
       </c>
       <c r="C28" s="24" t="s">
         <v>9</v>
@@ -3712,1241 +3625,1106 @@
         <v>13</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="I28" s="12"/>
-    </row>
-    <row r="29" spans="1:9" ht="150" x14ac:dyDescent="0.2">
-      <c r="A29" s="27">
-        <v>28</v>
-      </c>
-      <c r="B29" s="13">
-        <v>0.46388888888888902</v>
+        <v>60</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="27"/>
+      <c r="B29" s="4">
+        <v>0.42986111111111114</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="D29" s="9"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6">
+        <v>1</v>
+      </c>
+      <c r="G29" s="6"/>
+      <c r="H29" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="27">
+        <v>15</v>
+      </c>
+      <c r="B30" s="13">
+        <v>0.43056712962962962</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I30" s="12"/>
+    </row>
+    <row r="31" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="27"/>
+      <c r="B31" s="4">
+        <v>0.43472222222222212</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6">
+        <v>1</v>
+      </c>
+      <c r="G31" s="6"/>
+      <c r="H31" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="12"/>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:10" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="27">
+        <v>16</v>
+      </c>
+      <c r="B32" s="13">
+        <v>0.43542824074074066</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I32" s="12"/>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="27"/>
+      <c r="B33" s="4">
+        <v>0.43680555555555556</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6"/>
+      <c r="H33" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I33" s="12"/>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="1:10" ht="138" x14ac:dyDescent="0.3">
+      <c r="A34" s="27">
+        <v>17</v>
+      </c>
+      <c r="B34" s="13">
+        <v>0.43959490740740742</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I34" s="12"/>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="27"/>
+      <c r="B35" s="4">
+        <v>0.44444444444444414</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D35" s="9"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6">
+        <v>1</v>
+      </c>
+      <c r="G35" s="6"/>
+      <c r="H35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="12"/>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="1:10" ht="179.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="27">
+        <v>18</v>
+      </c>
+      <c r="B36" s="13">
+        <v>0.44515046296296268</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="27"/>
+      <c r="B37" s="4">
+        <v>0.45000000000000012</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D37" s="9"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6">
+        <v>1</v>
+      </c>
+      <c r="G37" s="6"/>
+      <c r="H37" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" s="12"/>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="1:10" ht="138" x14ac:dyDescent="0.3">
+      <c r="A38" s="27">
+        <v>19</v>
+      </c>
+      <c r="B38" s="13">
+        <v>0.45070601851851866</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I38" s="12"/>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="27"/>
+      <c r="B39" s="4">
+        <v>0.4555555555555551</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D39" s="9"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6">
+        <v>1</v>
+      </c>
+      <c r="G39" s="6"/>
+      <c r="H39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="12"/>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="1:10" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="27">
+        <v>20</v>
+      </c>
+      <c r="B40" s="13">
+        <v>0.45626157407407364</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I40" s="12"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="27"/>
+      <c r="B41" s="4">
+        <v>0.4597222222222222</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6">
+        <v>1</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I41" s="12"/>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="1:10" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="27">
+        <v>21</v>
+      </c>
+      <c r="B42" s="13">
+        <v>0.46042824074074074</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I42" s="12"/>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="27"/>
+      <c r="B43" s="4">
+        <v>0.46527777777777812</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6">
+        <v>1</v>
+      </c>
+      <c r="G43" s="6"/>
+      <c r="H43" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="12"/>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="27">
+        <v>22</v>
+      </c>
+      <c r="B44" s="13">
+        <v>0.46598379629629666</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I44" s="12"/>
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="27"/>
+      <c r="B45" s="4">
+        <v>0.4708333333333331</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D45" s="9"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6">
+        <v>1</v>
+      </c>
+      <c r="G45" s="6"/>
+      <c r="H45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I45" s="12"/>
+      <c r="J45" s="3"/>
+    </row>
+    <row r="46" spans="1:10" ht="138" x14ac:dyDescent="0.3">
+      <c r="A46" s="27">
+        <v>23</v>
+      </c>
+      <c r="B46" s="13">
+        <v>0.47153935185185164</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A30" s="27">
-        <v>29</v>
-      </c>
-      <c r="B30" s="13">
-        <v>0.46666666666666701</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E30" s="10" t="s">
+      <c r="E46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I46" s="12"/>
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="27"/>
+      <c r="B47" s="4">
+        <v>0.47638888888888914</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D47" s="9"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="6">
+        <v>1</v>
+      </c>
+      <c r="G47" s="6"/>
+      <c r="H47" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="I30" s="12"/>
-    </row>
-    <row r="31" spans="1:9" ht="150" x14ac:dyDescent="0.2">
-      <c r="A31" s="27">
-        <v>30</v>
-      </c>
-      <c r="B31" s="13">
-        <v>0.469444444444444</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="9" t="s">
+      <c r="I47" s="12"/>
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" spans="1:10" ht="69" x14ac:dyDescent="0.3">
+      <c r="A48" s="27">
         <v>24</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="B48" s="13">
+        <v>0.47709490740740768</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I48" s="12"/>
+      <c r="J48" s="3"/>
+    </row>
+    <row r="49" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="27"/>
+      <c r="B49" s="4">
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D49" s="9"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6">
+        <v>1</v>
+      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I49" s="12"/>
+      <c r="J49" s="3"/>
+    </row>
+    <row r="50" spans="1:10" ht="138" x14ac:dyDescent="0.3">
+      <c r="A50" s="27">
         <v>25</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="I31" s="12"/>
-    </row>
-    <row r="32" spans="1:9" ht="120" x14ac:dyDescent="0.2">
-      <c r="A32" s="27">
-        <v>31</v>
-      </c>
-      <c r="B32" s="13">
-        <v>0.47222222222222199</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="I32" s="12"/>
-    </row>
-    <row r="33" spans="1:9" ht="105" x14ac:dyDescent="0.2">
-      <c r="A33" s="27">
-        <v>32</v>
-      </c>
-      <c r="B33" s="13">
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="I33" s="12"/>
-    </row>
-    <row r="34" spans="1:9" ht="150" x14ac:dyDescent="0.2">
-      <c r="A34" s="27">
-        <v>33</v>
-      </c>
-      <c r="B34" s="13">
-        <v>0.47777777777777802</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="I34" s="12"/>
-    </row>
-    <row r="35" spans="1:9" ht="105" x14ac:dyDescent="0.2">
-      <c r="A35" s="27">
-        <v>34</v>
-      </c>
-      <c r="B35" s="15">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A36" s="27">
-        <v>35</v>
-      </c>
-      <c r="B36" s="15">
-        <v>0.48194444444444445</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="I36" s="12"/>
-    </row>
-    <row r="37" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A37" s="27">
-        <v>36</v>
-      </c>
-      <c r="B37" s="15">
-        <v>0.484722222222222</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="I37" s="12"/>
-    </row>
-    <row r="38" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A38" s="27">
-        <v>37</v>
-      </c>
-      <c r="B38" s="15">
-        <v>0.48749999999999999</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="I38" s="12"/>
-    </row>
-    <row r="39" spans="1:9" ht="120" x14ac:dyDescent="0.2">
-      <c r="A39" s="27">
-        <v>38</v>
-      </c>
-      <c r="B39" s="15">
-        <v>0.49027777777777798</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="I39" s="12"/>
-    </row>
-    <row r="40" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A40" s="27">
-        <v>39</v>
-      </c>
-      <c r="B40" s="15">
-        <v>0.49305555555555503</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="I40" s="12"/>
-    </row>
-    <row r="41" spans="1:9" ht="120" x14ac:dyDescent="0.2">
-      <c r="A41" s="27">
-        <v>40</v>
-      </c>
-      <c r="B41" s="15">
-        <v>0.49583333333333302</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="I41" s="12"/>
-    </row>
-    <row r="42" spans="1:9" ht="120" x14ac:dyDescent="0.2">
-      <c r="A42" s="27">
-        <v>41</v>
-      </c>
-      <c r="B42" s="15">
-        <v>0.49861111111111101</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="H42" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="I42" s="12"/>
-    </row>
-    <row r="43" spans="1:9" ht="180" x14ac:dyDescent="0.2">
-      <c r="A43" s="27">
-        <v>42</v>
-      </c>
-      <c r="B43" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F43" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I43" s="12" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A44" s="27">
-        <v>43</v>
-      </c>
-      <c r="B44" s="13">
-        <v>0.50277777777777777</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="I44" s="12"/>
-    </row>
-    <row r="45" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A45" s="27">
-        <v>44</v>
-      </c>
-      <c r="B45" s="13">
-        <v>0.50555555555555598</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="I45" s="12"/>
-    </row>
-    <row r="46" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A46" s="27">
-        <v>45</v>
-      </c>
-      <c r="B46" s="13">
-        <v>0.50833333333333297</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="I46" s="12"/>
-    </row>
-    <row r="47" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A47" s="27">
-        <v>46</v>
-      </c>
-      <c r="B47" s="13">
-        <v>0.51111111111111096</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="I47" s="12"/>
-    </row>
-    <row r="48" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A48" s="27">
-        <v>47</v>
-      </c>
-      <c r="B48" s="13">
-        <v>0.51388888888888895</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="I48" s="12"/>
-    </row>
-    <row r="49" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A49" s="27">
-        <v>48</v>
-      </c>
-      <c r="B49" s="13">
-        <v>0.51666666666666705</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I49" s="12"/>
-    </row>
-    <row r="50" spans="1:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="A50" s="27">
-        <v>49</v>
-      </c>
       <c r="B50" s="13">
-        <v>0.51944444444444404</v>
+        <v>0.48126157407407411</v>
       </c>
       <c r="C50" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>34</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>181</v>
+        <v>100</v>
       </c>
       <c r="I50" s="12"/>
-    </row>
-    <row r="51" spans="1:9" ht="150" x14ac:dyDescent="0.2">
-      <c r="A51" s="27">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13">
-        <v>0.52083333333333337</v>
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="27"/>
+      <c r="B51" s="4">
+        <v>0.4861111111111111</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>182</v>
+        <v>275</v>
+      </c>
+      <c r="D51" s="9"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="6">
+        <v>1</v>
       </c>
       <c r="G51" s="6"/>
-      <c r="H51" s="7" t="s">
-        <v>183</v>
+      <c r="H51" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="I51" s="12"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" s="27"/>
+      <c r="J51" s="3"/>
+    </row>
+    <row r="52" spans="1:10" ht="289.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="27">
+        <v>26</v>
+      </c>
       <c r="B52" s="13">
-        <v>0.5229166666666667</v>
+        <v>0.48681712962962964</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>276</v>
-      </c>
-      <c r="D52" s="9"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="6">
-        <v>56</v>
-      </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="12"/>
-    </row>
-    <row r="53" spans="1:9" ht="120" x14ac:dyDescent="0.2">
-      <c r="A53" s="27">
-        <v>51</v>
-      </c>
-      <c r="B53" s="13">
-        <v>0.5625</v>
+        <v>9</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J52" s="3"/>
+    </row>
+    <row r="53" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="27"/>
+      <c r="B53" s="4">
+        <v>0.49166666666666614</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E53" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="D53" s="9"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6">
+        <v>1</v>
+      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I53" s="12"/>
+      <c r="J53" s="3"/>
+    </row>
+    <row r="54" spans="1:10" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="27">
+        <v>27</v>
+      </c>
+      <c r="B54" s="13">
+        <v>0.49237268518518468</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I54" s="12"/>
+      <c r="J54" s="3"/>
+    </row>
+    <row r="55" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="27"/>
+      <c r="B55" s="4">
+        <v>0.49722222222222212</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D55" s="9"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="6">
+        <v>1</v>
+      </c>
+      <c r="G55" s="6"/>
+      <c r="H55" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F53" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="G53" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="H53" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="I53" s="12" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A54" s="27">
-        <v>52</v>
-      </c>
-      <c r="B54" s="13">
-        <v>0.56527777777777777</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="9" t="s">
+      <c r="I55" s="12"/>
+      <c r="J55" s="3"/>
+    </row>
+    <row r="56" spans="1:10" ht="165.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="27">
+        <v>28</v>
+      </c>
+      <c r="B56" s="13">
+        <v>0.49792824074074066</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E56" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="27"/>
+      <c r="B57" s="4">
+        <v>0.50138888888888888</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D57" s="9"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="6">
+        <v>1</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" s="12"/>
+      <c r="J57" s="3"/>
+    </row>
+    <row r="58" spans="1:10" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="27">
+        <v>29</v>
+      </c>
+      <c r="B58" s="13">
+        <v>0.50209490740740736</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I58" s="12"/>
+      <c r="J58" s="3"/>
+    </row>
+    <row r="59" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="27"/>
+      <c r="B59" s="4">
+        <v>0.50694444444444409</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D59" s="9"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="6">
+        <v>1</v>
+      </c>
+      <c r="G59" s="6"/>
+      <c r="H59" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59" s="12"/>
+      <c r="J59" s="3"/>
+    </row>
+    <row r="60" spans="1:10" ht="138" x14ac:dyDescent="0.3">
+      <c r="A60" s="27">
+        <v>30</v>
+      </c>
+      <c r="B60" s="13">
+        <v>0.50765046296296257</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I60" s="12"/>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="27"/>
+      <c r="B61" s="4">
+        <v>0.51250000000000007</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D61" s="9"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="6">
+        <v>1</v>
+      </c>
+      <c r="G61" s="6"/>
+      <c r="H61" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F54" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="G54" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="H54" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="I54" s="12" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A55" s="27">
-        <v>53</v>
-      </c>
-      <c r="B55" s="13">
-        <v>0.56805555555555598</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="G55" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="H55" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="I55" s="12"/>
-    </row>
-    <row r="56" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A56" s="27">
-        <v>54</v>
-      </c>
-      <c r="B56" s="13">
-        <v>0.57083333333333297</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="G56" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="H56" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="I56" s="12" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A57" s="27">
-        <v>55</v>
-      </c>
-      <c r="B57" s="13">
-        <v>0.57222222222222219</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="G57" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="H57" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="I57" s="12" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="180" x14ac:dyDescent="0.2">
-      <c r="A58" s="27">
-        <v>56</v>
-      </c>
-      <c r="B58" s="13">
-        <v>0.57361111111111096</v>
-      </c>
-      <c r="C58" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="E58" s="10" t="s">
+      <c r="I61" s="12"/>
+      <c r="J61" s="3"/>
+    </row>
+    <row r="62" spans="1:10" ht="138" x14ac:dyDescent="0.3">
+      <c r="A62" s="27">
+        <v>31</v>
+      </c>
+      <c r="B62" s="13">
+        <v>0.51320601851851855</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I62" s="12"/>
+      <c r="J62" s="3"/>
+    </row>
+    <row r="63" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="27"/>
+      <c r="B63" s="4">
+        <v>0.51805555555555516</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D63" s="9"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="6">
+        <v>1</v>
+      </c>
+      <c r="G63" s="6"/>
+      <c r="H63" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="G58" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="H58" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="I58" s="12"/>
-    </row>
-    <row r="59" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A59" s="27">
-        <v>57</v>
-      </c>
-      <c r="B59" s="13">
-        <v>0.57638888888888895</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="9" t="s">
+      <c r="I63" s="12"/>
+      <c r="J63" s="3"/>
+    </row>
+    <row r="64" spans="1:10" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="27">
+        <v>32</v>
+      </c>
+      <c r="B64" s="13">
+        <v>0.51876157407407364</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="I64" s="12"/>
+      <c r="J64" s="3"/>
+    </row>
+    <row r="65" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="27"/>
+      <c r="B65" s="4">
+        <v>0.47708333333333358</v>
+      </c>
+      <c r="C65" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D65" s="9"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="6">
+        <v>1</v>
+      </c>
+      <c r="G65" s="6"/>
+      <c r="H65" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I65" s="12"/>
+      <c r="J65" s="3"/>
+    </row>
+    <row r="66" spans="1:10" ht="151.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A66" s="27">
+        <v>33</v>
+      </c>
+      <c r="B66" s="13">
+        <v>0.47778935185185212</v>
+      </c>
+      <c r="C66" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E66" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F59" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="G59" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="H59" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="I59" s="12"/>
-    </row>
-    <row r="60" spans="1:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="A60" s="27">
-        <v>58</v>
-      </c>
-      <c r="B60" s="13">
-        <v>0.57916666666666705</v>
-      </c>
-      <c r="C60" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E60" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="G60" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="H60" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="I60" s="12"/>
-    </row>
-    <row r="61" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="A61" s="27">
-        <v>59</v>
-      </c>
-      <c r="B61" s="13">
-        <v>0.58194444444444404</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="E61" s="5" t="s">
+      <c r="F66" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I66" s="12"/>
+      <c r="J66" s="3"/>
+    </row>
+    <row r="67" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="27"/>
+      <c r="B67" s="4">
+        <v>0.47847222222222224</v>
+      </c>
+      <c r="C67" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D67" s="9"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="6">
+        <v>1</v>
+      </c>
+      <c r="G67" s="6"/>
+      <c r="H67" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I67" s="12"/>
+      <c r="J67" s="3"/>
+    </row>
+    <row r="68" spans="1:10" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A68" s="27">
         <v>34</v>
       </c>
-      <c r="F61" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="G61" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="H61" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="I61" s="12"/>
-    </row>
-    <row r="62" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A62" s="27">
-        <v>60</v>
-      </c>
-      <c r="B62" s="13">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="C62" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F62" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="G62" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="H62" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A63" s="27">
-        <v>61</v>
-      </c>
-      <c r="B63" s="13">
-        <v>0.58611111111111114</v>
-      </c>
-      <c r="C63" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="G63" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="H63" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="I63" s="12"/>
-    </row>
-    <row r="64" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A64" s="27">
-        <v>62</v>
-      </c>
-      <c r="B64" s="13">
-        <v>0.58888888888888902</v>
-      </c>
-      <c r="C64" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="G64" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="H64" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="I64" s="12"/>
-    </row>
-    <row r="65" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A65" s="27">
-        <v>63</v>
-      </c>
-      <c r="B65" s="13">
-        <v>0.59166666666666667</v>
-      </c>
-      <c r="C65" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E65" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="G65" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="H65" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="I65" s="12"/>
-    </row>
-    <row r="66" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A66" s="27">
-        <v>64</v>
-      </c>
-      <c r="B66" s="13">
-        <v>0.59305555555555556</v>
-      </c>
-      <c r="C66" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="G66" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="H66" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="I66" s="12"/>
-    </row>
-    <row r="67" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A67" s="27">
-        <v>65</v>
-      </c>
-      <c r="B67" s="13">
-        <v>0.594444444444444</v>
-      </c>
-      <c r="C67" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="G67" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="H67" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="I67" s="12"/>
-    </row>
-    <row r="68" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A68" s="27">
-        <v>66</v>
-      </c>
-      <c r="B68" s="13">
-        <v>0.59722222222222199</v>
+      <c r="B68" s="15">
+        <v>0.47917824074074078</v>
       </c>
       <c r="C68" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F68" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="G68" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="H68" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="I68" s="12"/>
-    </row>
-    <row r="69" spans="1:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="A69" s="27">
-        <v>67</v>
-      </c>
-      <c r="B69" s="13">
-        <v>0.6</v>
+      <c r="F68" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="J68" s="3"/>
+    </row>
+    <row r="69" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="27"/>
+      <c r="B69" s="4">
+        <v>0.48125000000000001</v>
       </c>
       <c r="C69" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="G69" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="H69" s="19" t="s">
-        <v>238</v>
+        <v>275</v>
+      </c>
+      <c r="D69" s="9"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="6">
+        <v>1</v>
+      </c>
+      <c r="G69" s="6"/>
+      <c r="H69" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="I69" s="12"/>
-    </row>
-    <row r="70" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+      <c r="J69" s="3"/>
+    </row>
+    <row r="70" spans="1:10" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A70" s="27">
-        <v>68</v>
-      </c>
-      <c r="B70" s="13">
-        <v>0.60277777777777797</v>
+        <v>35</v>
+      </c>
+      <c r="B70" s="15">
+        <v>0.48195601851851855</v>
       </c>
       <c r="C70" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D70" s="9" t="s">
-        <v>239</v>
+      <c r="D70" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>14</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="G70" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="H70" s="19" t="s">
-        <v>241</v>
+        <v>136</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="I70" s="12"/>
-    </row>
-    <row r="71" spans="1:9" ht="150" x14ac:dyDescent="0.2">
-      <c r="A71" s="27">
-        <v>69</v>
-      </c>
-      <c r="B71" s="13">
-        <v>0.60416666666666663</v>
+      <c r="J70" s="3"/>
+    </row>
+    <row r="71" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="27"/>
+      <c r="B71" s="4">
+        <v>0.48402777777777756</v>
       </c>
       <c r="C71" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E71" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="D71" s="9"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="6">
+        <v>1</v>
+      </c>
+      <c r="G71" s="6"/>
+      <c r="H71" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F71" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="G71" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="H71" s="19" t="s">
-        <v>244</v>
-      </c>
       <c r="I71" s="12"/>
-    </row>
-    <row r="72" spans="1:9" ht="195" x14ac:dyDescent="0.2">
+      <c r="J71" s="3"/>
+    </row>
+    <row r="72" spans="1:10" ht="69" x14ac:dyDescent="0.3">
       <c r="A72" s="27">
-        <v>70</v>
-      </c>
-      <c r="B72" s="13">
-        <v>0.6069444444444444</v>
+        <v>36</v>
+      </c>
+      <c r="B72" s="15">
+        <v>0.48473379629629609</v>
       </c>
       <c r="C72" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>13</v>
+        <v>139</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="G72" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="H72" s="19" t="s">
-        <v>247</v>
+        <v>140</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="I72" s="12"/>
-    </row>
-    <row r="73" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A73" s="27">
-        <v>71</v>
-      </c>
-      <c r="B73" s="13">
-        <v>0.60972222222222205</v>
+      <c r="J72" s="3"/>
+    </row>
+    <row r="73" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="27"/>
+      <c r="B73" s="4">
+        <v>0.48680555555555555</v>
       </c>
       <c r="C73" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="G73" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="H73" s="19" t="s">
-        <v>250</v>
+        <v>275</v>
+      </c>
+      <c r="D73" s="9"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="6">
+        <v>1</v>
+      </c>
+      <c r="G73" s="6"/>
+      <c r="H73" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="I73" s="12"/>
-    </row>
-    <row r="74" spans="1:9" ht="75" x14ac:dyDescent="0.2">
+      <c r="J73" s="3"/>
+    </row>
+    <row r="74" spans="1:10" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A74" s="27">
-        <v>72</v>
-      </c>
-      <c r="B74" s="13">
-        <v>0.61249999999999993</v>
+        <v>37</v>
+      </c>
+      <c r="B74" s="15">
+        <v>0.48751157407407408</v>
       </c>
       <c r="C74" s="24" t="s">
         <v>9</v>
@@ -4958,239 +4736,2351 @@
         <v>25</v>
       </c>
       <c r="F74" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I74" s="12"/>
+      <c r="J74" s="3"/>
+    </row>
+    <row r="75" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="27"/>
+      <c r="B75" s="4">
+        <v>0.48958333333333354</v>
+      </c>
+      <c r="C75" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D75" s="9"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="6">
+        <v>1</v>
+      </c>
+      <c r="G75" s="6"/>
+      <c r="H75" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I75" s="12"/>
+      <c r="J75" s="3"/>
+    </row>
+    <row r="76" spans="1:10" ht="138" x14ac:dyDescent="0.3">
+      <c r="A76" s="27">
+        <v>38</v>
+      </c>
+      <c r="B76" s="15">
+        <v>0.49028935185185207</v>
+      </c>
+      <c r="C76" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I76" s="12"/>
+      <c r="J76" s="3"/>
+    </row>
+    <row r="77" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A77" s="27"/>
+      <c r="B77" s="4">
+        <v>0.49236111111111058</v>
+      </c>
+      <c r="C77" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D77" s="9"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="6">
+        <v>1</v>
+      </c>
+      <c r="G77" s="6"/>
+      <c r="H77" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I77" s="12"/>
+      <c r="J77" s="3"/>
+    </row>
+    <row r="78" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A78" s="27">
+        <v>39</v>
+      </c>
+      <c r="B78" s="15">
+        <v>0.49306712962962912</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I78" s="12"/>
+      <c r="J78" s="3"/>
+    </row>
+    <row r="79" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="27"/>
+      <c r="B79" s="4">
+        <v>0.49513888888888857</v>
+      </c>
+      <c r="C79" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D79" s="9"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="6">
+        <v>1</v>
+      </c>
+      <c r="G79" s="6"/>
+      <c r="H79" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" s="12"/>
+      <c r="J79" s="3"/>
+    </row>
+    <row r="80" spans="1:10" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A80" s="27">
+        <v>40</v>
+      </c>
+      <c r="B80" s="15">
+        <v>0.49584490740740711</v>
+      </c>
+      <c r="C80" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I80" s="12"/>
+      <c r="J80" s="3"/>
+    </row>
+    <row r="81" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A81" s="27"/>
+      <c r="B81" s="4">
+        <v>0.49791666666666656</v>
+      </c>
+      <c r="C81" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D81" s="9"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="6">
+        <v>1</v>
+      </c>
+      <c r="G81" s="6"/>
+      <c r="H81" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I81" s="12"/>
+      <c r="J81" s="3"/>
+    </row>
+    <row r="82" spans="1:10" ht="138" x14ac:dyDescent="0.3">
+      <c r="A82" s="27">
+        <v>41</v>
+      </c>
+      <c r="B82" s="15">
+        <v>0.4986226851851851</v>
+      </c>
+      <c r="C82" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="I82" s="12"/>
+      <c r="J82" s="3"/>
+    </row>
+    <row r="83" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="27"/>
+      <c r="B83" s="4">
+        <v>0.49930555555555556</v>
+      </c>
+      <c r="C83" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D83" s="9"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="6">
+        <v>1</v>
+      </c>
+      <c r="G83" s="6"/>
+      <c r="H83" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I83" s="12"/>
+      <c r="J83" s="3"/>
+    </row>
+    <row r="84" spans="1:10" ht="193.2" x14ac:dyDescent="0.3">
+      <c r="A84" s="27">
+        <v>42</v>
+      </c>
+      <c r="B84" s="13">
+        <v>0.50001157407407404</v>
+      </c>
+      <c r="C84" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F84" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="I84" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="J84" s="3"/>
+    </row>
+    <row r="85" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A85" s="27"/>
+      <c r="B85" s="4">
+        <v>0.50208333333333333</v>
+      </c>
+      <c r="C85" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D85" s="9"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="6">
+        <v>1</v>
+      </c>
+      <c r="G85" s="6"/>
+      <c r="H85" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I85" s="12"/>
+      <c r="J85" s="3"/>
+    </row>
+    <row r="86" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A86" s="27">
+        <v>43</v>
+      </c>
+      <c r="B86" s="13">
+        <v>0.50278935185185181</v>
+      </c>
+      <c r="C86" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I86" s="12"/>
+      <c r="J86" s="3"/>
+    </row>
+    <row r="87" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A87" s="27"/>
+      <c r="B87" s="4">
+        <v>0.50486111111111154</v>
+      </c>
+      <c r="C87" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D87" s="9"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="6">
+        <v>1</v>
+      </c>
+      <c r="G87" s="6"/>
+      <c r="H87" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I87" s="12"/>
+      <c r="J87" s="3"/>
+    </row>
+    <row r="88" spans="1:10" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A88" s="27">
+        <v>44</v>
+      </c>
+      <c r="B88" s="13">
+        <v>0.50556712962963002</v>
+      </c>
+      <c r="C88" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="I88" s="12"/>
+      <c r="J88" s="3"/>
+    </row>
+    <row r="89" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="27"/>
+      <c r="B89" s="4">
+        <v>0.50763888888888853</v>
+      </c>
+      <c r="C89" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D89" s="9"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="6">
+        <v>1</v>
+      </c>
+      <c r="G89" s="6"/>
+      <c r="H89" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I89" s="12"/>
+      <c r="J89" s="3"/>
+    </row>
+    <row r="90" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A90" s="27">
+        <v>45</v>
+      </c>
+      <c r="B90" s="13">
+        <v>0.50834490740740701</v>
+      </c>
+      <c r="C90" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="I90" s="12"/>
+      <c r="J90" s="3"/>
+    </row>
+    <row r="91" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A91" s="27"/>
+      <c r="B91" s="4">
+        <v>0.51041666666666652</v>
+      </c>
+      <c r="C91" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D91" s="9"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="6">
+        <v>1</v>
+      </c>
+      <c r="G91" s="6"/>
+      <c r="H91" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I91" s="12"/>
+      <c r="J91" s="3"/>
+    </row>
+    <row r="92" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A92" s="27">
+        <v>46</v>
+      </c>
+      <c r="B92" s="13">
+        <v>0.511122685185185</v>
+      </c>
+      <c r="C92" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="I92" s="12"/>
+      <c r="J92" s="3"/>
+    </row>
+    <row r="93" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A93" s="27"/>
+      <c r="B93" s="4">
+        <v>0.51319444444444451</v>
+      </c>
+      <c r="C93" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D93" s="9"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="6">
+        <v>1</v>
+      </c>
+      <c r="G93" s="6"/>
+      <c r="H93" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" s="12"/>
+      <c r="J93" s="3"/>
+    </row>
+    <row r="94" spans="1:10" ht="69" x14ac:dyDescent="0.3">
+      <c r="A94" s="27">
+        <v>47</v>
+      </c>
+      <c r="B94" s="13">
+        <v>0.51390046296296299</v>
+      </c>
+      <c r="C94" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="I94" s="12"/>
+      <c r="J94" s="3"/>
+    </row>
+    <row r="95" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A95" s="27"/>
+      <c r="B95" s="4">
+        <v>0.51597222222222261</v>
+      </c>
+      <c r="C95" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D95" s="9"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="6">
+        <v>1</v>
+      </c>
+      <c r="G95" s="6"/>
+      <c r="H95" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I95" s="12"/>
+      <c r="J95" s="3"/>
+    </row>
+    <row r="96" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A96" s="27">
+        <v>48</v>
+      </c>
+      <c r="B96" s="13">
+        <v>0.51667824074074109</v>
+      </c>
+      <c r="C96" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="I96" s="12"/>
+      <c r="J96" s="3"/>
+    </row>
+    <row r="97" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A97" s="27"/>
+      <c r="B97" s="4">
+        <v>0.5187499999999996</v>
+      </c>
+      <c r="C97" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D97" s="9"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="6">
+        <v>1</v>
+      </c>
+      <c r="G97" s="6"/>
+      <c r="H97" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I97" s="12"/>
+      <c r="J97" s="3"/>
+    </row>
+    <row r="98" spans="1:10" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A98" s="27">
+        <v>49</v>
+      </c>
+      <c r="B98" s="13">
+        <v>0.51945601851851808</v>
+      </c>
+      <c r="C98" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="I98" s="12"/>
+      <c r="J98" s="3"/>
+    </row>
+    <row r="99" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="27"/>
+      <c r="B99" s="4">
+        <v>0.52013888888888893</v>
+      </c>
+      <c r="C99" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D99" s="9"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="6">
+        <v>1</v>
+      </c>
+      <c r="G99" s="6"/>
+      <c r="H99" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" s="12"/>
+      <c r="J99" s="3"/>
+    </row>
+    <row r="100" spans="1:10" ht="138" x14ac:dyDescent="0.3">
+      <c r="A100" s="27">
+        <v>50</v>
+      </c>
+      <c r="B100" s="13">
+        <v>0.52084490740740741</v>
+      </c>
+      <c r="C100" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="G100" s="6"/>
+      <c r="H100" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="I100" s="12"/>
+      <c r="J100" s="3"/>
+    </row>
+    <row r="101" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="27"/>
+      <c r="B101" s="13">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="C101" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D101" s="9"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="6">
+        <v>57</v>
+      </c>
+      <c r="G101" s="6"/>
+      <c r="H101" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="I101" s="12"/>
+      <c r="J101" s="3"/>
+    </row>
+    <row r="102" spans="1:10" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A102" s="27">
+        <v>51</v>
+      </c>
+      <c r="B102" s="13">
+        <v>0.56251157407407404</v>
+      </c>
+      <c r="C102" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G102" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="H102" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="I102" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="J102" s="3"/>
+    </row>
+    <row r="103" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="27"/>
+      <c r="B103" s="4">
+        <v>0.56458333333333333</v>
+      </c>
+      <c r="C103" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D103" s="9"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="6">
+        <v>1</v>
+      </c>
+      <c r="G103" s="6"/>
+      <c r="H103" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I103" s="12"/>
+      <c r="J103" s="3"/>
+    </row>
+    <row r="104" spans="1:10" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="27">
+        <v>52</v>
+      </c>
+      <c r="B104" s="13">
+        <v>0.56528935185185181</v>
+      </c>
+      <c r="C104" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="G104" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="H104" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="I104" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="J104" s="3"/>
+    </row>
+    <row r="105" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="27"/>
+      <c r="B105" s="4">
+        <v>0.56736111111111154</v>
+      </c>
+      <c r="C105" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D105" s="9"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="6">
+        <v>1</v>
+      </c>
+      <c r="G105" s="6"/>
+      <c r="H105" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="I105" s="12"/>
+      <c r="J105" s="3"/>
+    </row>
+    <row r="106" spans="1:10" ht="69" x14ac:dyDescent="0.3">
+      <c r="A106" s="27">
+        <v>53</v>
+      </c>
+      <c r="B106" s="13">
+        <v>0.56806712962963002</v>
+      </c>
+      <c r="C106" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G106" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="H106" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="I106" s="12"/>
+      <c r="J106" s="3"/>
+    </row>
+    <row r="107" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A107" s="27"/>
+      <c r="B107" s="4">
+        <v>0.57013888888888853</v>
+      </c>
+      <c r="C107" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D107" s="9"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="6">
+        <v>1</v>
+      </c>
+      <c r="G107" s="6"/>
+      <c r="H107" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I107" s="12"/>
+      <c r="J107" s="3"/>
+    </row>
+    <row r="108" spans="1:10" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A108" s="27">
+        <v>54</v>
+      </c>
+      <c r="B108" s="13">
+        <v>0.57084490740740701</v>
+      </c>
+      <c r="C108" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G108" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="H108" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="I108" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="J108" s="3"/>
+    </row>
+    <row r="109" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A109" s="27"/>
+      <c r="B109" s="4">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="C109" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D109" s="9"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="6">
+        <v>1</v>
+      </c>
+      <c r="G109" s="6"/>
+      <c r="H109" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I109" s="12"/>
+      <c r="J109" s="3"/>
+    </row>
+    <row r="110" spans="1:10" ht="69" x14ac:dyDescent="0.3">
+      <c r="A110" s="27">
+        <v>55</v>
+      </c>
+      <c r="B110" s="13">
+        <v>0.57223379629629623</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="G110" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="H110" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="I110" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="J110" s="3"/>
+    </row>
+    <row r="111" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A111" s="27"/>
+      <c r="B111" s="4">
+        <v>0.57291666666666652</v>
+      </c>
+      <c r="C111" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D111" s="9"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="6">
+        <v>1</v>
+      </c>
+      <c r="G111" s="6"/>
+      <c r="H111" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I111" s="12"/>
+      <c r="J111" s="3"/>
+    </row>
+    <row r="112" spans="1:10" ht="179.4" x14ac:dyDescent="0.3">
+      <c r="A112" s="27">
+        <v>56</v>
+      </c>
+      <c r="B112" s="13">
+        <v>0.573622685185185</v>
+      </c>
+      <c r="C112" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="G112" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="H112" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="I112" s="12"/>
+      <c r="J112" s="3"/>
+    </row>
+    <row r="113" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A113" s="27"/>
+      <c r="B113" s="4">
+        <v>0.57569444444444451</v>
+      </c>
+      <c r="C113" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D113" s="9"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="6">
+        <v>1</v>
+      </c>
+      <c r="G113" s="6"/>
+      <c r="H113" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I113" s="12"/>
+      <c r="J113" s="3"/>
+    </row>
+    <row r="114" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A114" s="27">
+        <v>57</v>
+      </c>
+      <c r="B114" s="13">
+        <v>0.57640046296296299</v>
+      </c>
+      <c r="C114" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="G114" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="H114" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="I114" s="12"/>
+      <c r="J114" s="3"/>
+    </row>
+    <row r="115" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A115" s="27"/>
+      <c r="B115" s="4">
+        <v>0.57847222222222261</v>
+      </c>
+      <c r="C115" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D115" s="9"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="6">
+        <v>1</v>
+      </c>
+      <c r="G115" s="6"/>
+      <c r="H115" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I115" s="12"/>
+      <c r="J115" s="3"/>
+    </row>
+    <row r="116" spans="1:10" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A116" s="27">
+        <v>58</v>
+      </c>
+      <c r="B116" s="13">
+        <v>0.57917824074074109</v>
+      </c>
+      <c r="C116" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="G116" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="H116" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="I116" s="12"/>
+      <c r="J116" s="3"/>
+    </row>
+    <row r="117" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A117" s="27"/>
+      <c r="B117" s="4">
+        <v>0.5812499999999996</v>
+      </c>
+      <c r="C117" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D117" s="9"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="6">
+        <v>1</v>
+      </c>
+      <c r="G117" s="6"/>
+      <c r="H117" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I117" s="12"/>
+      <c r="J117" s="3"/>
+    </row>
+    <row r="118" spans="1:10" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A118" s="27">
+        <v>59</v>
+      </c>
+      <c r="B118" s="13">
+        <v>0.58195601851851808</v>
+      </c>
+      <c r="C118" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F118" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="G118" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="H118" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="I118" s="12"/>
+      <c r="J118" s="3"/>
+    </row>
+    <row r="119" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A119" s="27"/>
+      <c r="B119" s="4">
+        <v>0.58263888888888893</v>
+      </c>
+      <c r="C119" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D119" s="9"/>
+      <c r="E119" s="5"/>
+      <c r="F119" s="6">
+        <v>1</v>
+      </c>
+      <c r="G119" s="6"/>
+      <c r="H119" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I119" s="12"/>
+      <c r="J119" s="3"/>
+    </row>
+    <row r="120" spans="1:10" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A120" s="27">
+        <v>60</v>
+      </c>
+      <c r="B120" s="13">
+        <v>0.58334490740740741</v>
+      </c>
+      <c r="C120" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F120" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G120" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="H120" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="I120" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="J120" s="3"/>
+    </row>
+    <row r="121" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A121" s="27"/>
+      <c r="B121" s="4">
+        <v>0.5854166666666667</v>
+      </c>
+      <c r="C121" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D121" s="9"/>
+      <c r="E121" s="5"/>
+      <c r="F121" s="6">
+        <v>1</v>
+      </c>
+      <c r="G121" s="6"/>
+      <c r="H121" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I121" s="12"/>
+      <c r="J121" s="3"/>
+    </row>
+    <row r="122" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A122" s="27">
+        <v>61</v>
+      </c>
+      <c r="B122" s="13">
+        <v>0.58612268518518518</v>
+      </c>
+      <c r="C122" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D122" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G122" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="H122" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="I122" s="12"/>
+      <c r="J122" s="3"/>
+    </row>
+    <row r="123" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A123" s="27"/>
+      <c r="B123" s="4">
+        <v>0.58819444444444458</v>
+      </c>
+      <c r="C123" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D123" s="9"/>
+      <c r="E123" s="5"/>
+      <c r="F123" s="6">
+        <v>1</v>
+      </c>
+      <c r="G123" s="6"/>
+      <c r="H123" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I123" s="12"/>
+      <c r="J123" s="3"/>
+    </row>
+    <row r="124" spans="1:10" ht="69" x14ac:dyDescent="0.3">
+      <c r="A124" s="27">
+        <v>62</v>
+      </c>
+      <c r="B124" s="13">
+        <v>0.58890046296296306</v>
+      </c>
+      <c r="C124" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="G124" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="H124" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="I124" s="12"/>
+      <c r="J124" s="3"/>
+    </row>
+    <row r="125" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A125" s="27"/>
+      <c r="B125" s="4">
+        <v>0.59097222222222223</v>
+      </c>
+      <c r="C125" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D125" s="9"/>
+      <c r="E125" s="5"/>
+      <c r="F125" s="6">
+        <v>1</v>
+      </c>
+      <c r="G125" s="6"/>
+      <c r="H125" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I125" s="12"/>
+      <c r="J125" s="3"/>
+    </row>
+    <row r="126" spans="1:10" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A126" s="27">
+        <v>63</v>
+      </c>
+      <c r="B126" s="13">
+        <v>0.59167824074074071</v>
+      </c>
+      <c r="C126" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="G126" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="H126" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="I126" s="12"/>
+      <c r="J126" s="3"/>
+    </row>
+    <row r="127" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A127" s="27"/>
+      <c r="B127" s="4">
+        <v>0.59236111111111112</v>
+      </c>
+      <c r="C127" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D127" s="9"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="6">
+        <v>1</v>
+      </c>
+      <c r="G127" s="6"/>
+      <c r="H127" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I127" s="12"/>
+      <c r="J127" s="3"/>
+    </row>
+    <row r="128" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A128" s="27">
+        <v>64</v>
+      </c>
+      <c r="B128" s="13">
+        <v>0.5930671296296296</v>
+      </c>
+      <c r="C128" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="G128" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H128" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="I128" s="12"/>
+      <c r="J128" s="3"/>
+    </row>
+    <row r="129" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A129" s="27"/>
+      <c r="B129" s="4">
+        <v>0.59374999999999956</v>
+      </c>
+      <c r="C129" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D129" s="9"/>
+      <c r="E129" s="5"/>
+      <c r="F129" s="6">
+        <v>1</v>
+      </c>
+      <c r="G129" s="6"/>
+      <c r="H129" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I129" s="12"/>
+      <c r="J129" s="3"/>
+    </row>
+    <row r="130" spans="1:10" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A130" s="27">
+        <v>65</v>
+      </c>
+      <c r="B130" s="13">
+        <v>0.59445601851851804</v>
+      </c>
+      <c r="C130" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F130" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="G130" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="H130" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="I130" s="12"/>
+      <c r="J130" s="3"/>
+    </row>
+    <row r="131" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A131" s="27"/>
+      <c r="B131" s="4">
+        <v>0.59652777777777755</v>
+      </c>
+      <c r="C131" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D131" s="9"/>
+      <c r="E131" s="5"/>
+      <c r="F131" s="6">
+        <v>1</v>
+      </c>
+      <c r="G131" s="6"/>
+      <c r="H131" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I131" s="12"/>
+      <c r="J131" s="3"/>
+    </row>
+    <row r="132" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A132" s="27">
+        <v>66</v>
+      </c>
+      <c r="B132" s="13">
+        <v>0.59723379629629603</v>
+      </c>
+      <c r="C132" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G132" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H132" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="I132" s="12"/>
+      <c r="J132" s="3"/>
+    </row>
+    <row r="133" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A133" s="27"/>
+      <c r="B133" s="4">
+        <v>0.59930555555555554</v>
+      </c>
+      <c r="C133" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D133" s="9"/>
+      <c r="E133" s="5"/>
+      <c r="F133" s="6">
+        <v>1</v>
+      </c>
+      <c r="G133" s="6"/>
+      <c r="H133" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I133" s="12"/>
+      <c r="J133" s="3"/>
+    </row>
+    <row r="134" spans="1:10" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A134" s="27">
+        <v>67</v>
+      </c>
+      <c r="B134" s="13">
+        <v>0.60001157407407402</v>
+      </c>
+      <c r="C134" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G134" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="H134" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="I134" s="12"/>
+      <c r="J134" s="3"/>
+    </row>
+    <row r="135" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A135" s="27"/>
+      <c r="B135" s="4">
+        <v>0.60208333333333353</v>
+      </c>
+      <c r="C135" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D135" s="9"/>
+      <c r="E135" s="5"/>
+      <c r="F135" s="6">
+        <v>1</v>
+      </c>
+      <c r="G135" s="6"/>
+      <c r="H135" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I135" s="12"/>
+      <c r="J135" s="3"/>
+    </row>
+    <row r="136" spans="1:10" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A136" s="27">
+        <v>68</v>
+      </c>
+      <c r="B136" s="13">
+        <v>0.60278935185185201</v>
+      </c>
+      <c r="C136" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="G136" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="H136" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="I136" s="12"/>
+      <c r="J136" s="3"/>
+    </row>
+    <row r="137" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A137" s="27"/>
+      <c r="B137" s="4">
+        <v>0.60347222222222219</v>
+      </c>
+      <c r="C137" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D137" s="9"/>
+      <c r="E137" s="5"/>
+      <c r="F137" s="6">
+        <v>1</v>
+      </c>
+      <c r="G137" s="6"/>
+      <c r="H137" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I137" s="12"/>
+      <c r="J137" s="3"/>
+    </row>
+    <row r="138" spans="1:10" ht="138" x14ac:dyDescent="0.3">
+      <c r="A138" s="27">
+        <v>69</v>
+      </c>
+      <c r="B138" s="13">
+        <v>0.60417824074074067</v>
+      </c>
+      <c r="C138" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G138" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="H138" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="I138" s="12"/>
+      <c r="J138" s="3"/>
+    </row>
+    <row r="139" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A139" s="27"/>
+      <c r="B139" s="4">
+        <v>0.60624999999999996</v>
+      </c>
+      <c r="C139" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D139" s="9"/>
+      <c r="E139" s="5"/>
+      <c r="F139" s="6">
+        <v>1</v>
+      </c>
+      <c r="G139" s="6"/>
+      <c r="H139" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I139" s="12"/>
+      <c r="J139" s="3"/>
+    </row>
+    <row r="140" spans="1:10" ht="207" x14ac:dyDescent="0.3">
+      <c r="A140" s="27">
+        <v>70</v>
+      </c>
+      <c r="B140" s="13">
+        <v>0.60695601851851844</v>
+      </c>
+      <c r="C140" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="G140" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="H140" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I140" s="12"/>
+      <c r="J140" s="3"/>
+    </row>
+    <row r="141" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A141" s="27"/>
+      <c r="B141" s="4">
+        <v>0.60902777777777761</v>
+      </c>
+      <c r="C141" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D141" s="9"/>
+      <c r="E141" s="5"/>
+      <c r="F141" s="6">
+        <v>1</v>
+      </c>
+      <c r="G141" s="6"/>
+      <c r="H141" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I141" s="12"/>
+      <c r="J141" s="3"/>
+    </row>
+    <row r="142" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A142" s="27">
+        <v>71</v>
+      </c>
+      <c r="B142" s="13">
+        <v>0.60973379629629609</v>
+      </c>
+      <c r="C142" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E142" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="G142" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="H142" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="I142" s="12"/>
+      <c r="J142" s="3"/>
+    </row>
+    <row r="143" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A143" s="27"/>
+      <c r="B143" s="4">
+        <v>0.61180555555555549</v>
+      </c>
+      <c r="C143" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D143" s="9"/>
+      <c r="E143" s="5"/>
+      <c r="F143" s="6">
+        <v>1</v>
+      </c>
+      <c r="G143" s="6"/>
+      <c r="H143" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I143" s="12"/>
+      <c r="J143" s="3"/>
+    </row>
+    <row r="144" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A144" s="27">
+        <v>72</v>
+      </c>
+      <c r="B144" s="13">
+        <v>0.61251157407407397</v>
+      </c>
+      <c r="C144" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F144" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="G74" s="18" t="s">
+      <c r="G144" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="H74" s="19" t="s">
+      <c r="H144" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="I74" s="12"/>
-    </row>
-    <row r="75" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A75" s="27">
+      <c r="I144" s="12"/>
+      <c r="J144" s="3"/>
+    </row>
+    <row r="145" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A145" s="27"/>
+      <c r="B145" s="4">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="C145" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D145" s="9"/>
+      <c r="E145" s="5"/>
+      <c r="F145" s="6">
+        <v>1</v>
+      </c>
+      <c r="G145" s="6"/>
+      <c r="H145" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I145" s="12"/>
+      <c r="J145" s="3"/>
+    </row>
+    <row r="146" spans="1:10" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A146" s="27">
         <v>73</v>
       </c>
-      <c r="B75" s="13">
-        <v>0.61527777777777781</v>
-      </c>
-      <c r="C75" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D75" s="9" t="s">
+      <c r="B146" s="13">
+        <v>0.61528935185185185</v>
+      </c>
+      <c r="C146" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D146" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E146" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F146" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="G75" s="18" t="s">
+      <c r="G146" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="H75" s="19" t="s">
+      <c r="H146" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="I75" s="12"/>
-    </row>
-    <row r="76" spans="1:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="A76" s="27">
+      <c r="I146" s="12"/>
+      <c r="J146" s="3"/>
+    </row>
+    <row r="147" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A147" s="27"/>
+      <c r="B147" s="4">
+        <v>0.61736111111111114</v>
+      </c>
+      <c r="C147" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D147" s="9"/>
+      <c r="E147" s="5"/>
+      <c r="F147" s="6">
+        <v>1</v>
+      </c>
+      <c r="G147" s="6"/>
+      <c r="H147" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I147" s="12"/>
+      <c r="J147" s="3"/>
+    </row>
+    <row r="148" spans="1:10" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A148" s="27">
         <v>74</v>
       </c>
-      <c r="B76" s="13">
-        <v>0.61805555555555558</v>
-      </c>
-      <c r="C76" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="9" t="s">
+      <c r="B148" s="13">
+        <v>0.61806712962962962</v>
+      </c>
+      <c r="C148" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D148" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E148" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F148" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="G76" s="18" t="s">
+      <c r="G148" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="H76" s="19" t="s">
+      <c r="H148" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="I76" s="12"/>
-    </row>
-    <row r="77" spans="1:9" ht="45" x14ac:dyDescent="0.2">
-      <c r="A77" s="27">
+      <c r="I148" s="12"/>
+      <c r="J148" s="3"/>
+    </row>
+    <row r="149" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A149" s="27"/>
+      <c r="B149" s="4">
+        <v>0.62013888888888891</v>
+      </c>
+      <c r="C149" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D149" s="9"/>
+      <c r="E149" s="5"/>
+      <c r="F149" s="6">
+        <v>1</v>
+      </c>
+      <c r="G149" s="6"/>
+      <c r="H149" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I149" s="12"/>
+      <c r="J149" s="3"/>
+    </row>
+    <row r="150" spans="1:10" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A150" s="27">
         <v>75</v>
       </c>
-      <c r="B77" s="13">
-        <v>0.62083333333333335</v>
-      </c>
-      <c r="C77" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77" s="9" t="s">
+      <c r="B150" s="13">
+        <v>0.62084490740740739</v>
+      </c>
+      <c r="C150" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E150" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F150" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G77" s="18" t="s">
+      <c r="G150" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="H77" s="19" t="s">
+      <c r="H150" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="I77" s="12"/>
-    </row>
-    <row r="78" spans="1:9" ht="90" x14ac:dyDescent="0.2">
-      <c r="A78" s="27">
+      <c r="I150" s="12"/>
+      <c r="J150" s="3"/>
+    </row>
+    <row r="151" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A151" s="27"/>
+      <c r="B151" s="4">
+        <v>0.62291666666666656</v>
+      </c>
+      <c r="C151" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D151" s="9"/>
+      <c r="E151" s="5"/>
+      <c r="F151" s="6">
+        <v>1</v>
+      </c>
+      <c r="G151" s="6"/>
+      <c r="H151" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="I151" s="12"/>
+      <c r="J151" s="3"/>
+    </row>
+    <row r="152" spans="1:10" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="A152" s="27">
         <v>76</v>
       </c>
-      <c r="B78" s="13">
-        <v>0.62361111111111101</v>
-      </c>
-      <c r="C78" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D78" s="9" t="s">
+      <c r="B152" s="13">
+        <v>0.62362268518518504</v>
+      </c>
+      <c r="C152" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="E152" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F78" s="6" t="s">
+      <c r="F152" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="G78" s="18" t="s">
+      <c r="G152" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="H78" s="19" t="s">
+      <c r="H152" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="I78" s="12"/>
-    </row>
-    <row r="79" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="A79" s="27">
+      <c r="I152" s="12"/>
+      <c r="J152" s="3"/>
+    </row>
+    <row r="153" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A153" s="27"/>
+      <c r="B153" s="4">
+        <v>0.62430555555555556</v>
+      </c>
+      <c r="C153" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D153" s="9"/>
+      <c r="E153" s="5"/>
+      <c r="F153" s="6">
+        <v>1</v>
+      </c>
+      <c r="G153" s="6"/>
+      <c r="H153" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I153" s="12"/>
+      <c r="J153" s="3"/>
+    </row>
+    <row r="154" spans="1:10" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A154" s="27">
         <v>77</v>
       </c>
-      <c r="B79" s="13">
-        <v>0.625</v>
-      </c>
-      <c r="C79" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="9" t="s">
+      <c r="B154" s="13">
+        <v>0.62501157407407404</v>
+      </c>
+      <c r="C154" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D154" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="E154" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F79" s="18" t="s">
+      <c r="F154" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="G79" s="18" t="s">
+      <c r="G154" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="H79" s="22"/>
-      <c r="I79" s="12" t="s">
+      <c r="H154" s="22"/>
+      <c r="I154" s="12" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" ht="105" x14ac:dyDescent="0.2">
-      <c r="A80" s="27">
+      <c r="J154" s="3"/>
+    </row>
+    <row r="155" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A155" s="27"/>
+      <c r="B155" s="4">
+        <v>0.63472222222222219</v>
+      </c>
+      <c r="C155" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D155" s="9"/>
+      <c r="E155" s="5"/>
+      <c r="F155" s="6">
+        <v>1</v>
+      </c>
+      <c r="G155" s="6"/>
+      <c r="H155" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I155" s="12"/>
+      <c r="J155" s="3"/>
+    </row>
+    <row r="156" spans="1:10" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A156" s="27">
         <v>78</v>
       </c>
-      <c r="B80" s="13">
-        <v>0.63541666666666663</v>
-      </c>
-      <c r="C80" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D80" s="9" t="s">
+      <c r="B156" s="13">
+        <v>0.63542824074074067</v>
+      </c>
+      <c r="C156" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D156" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="E156" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F80" s="18" t="s">
+      <c r="F156" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="G80" s="18" t="s">
+      <c r="G156" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="H80" s="22"/>
-      <c r="I80" s="12" t="s">
+      <c r="H156" s="22"/>
+      <c r="I156" s="12" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" ht="120" x14ac:dyDescent="0.2">
-      <c r="A81" s="27">
+      <c r="J156" s="3"/>
+    </row>
+    <row r="157" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A157" s="27"/>
+      <c r="B157" s="4">
+        <v>0.63819444444444451</v>
+      </c>
+      <c r="C157" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D157" s="9"/>
+      <c r="E157" s="5"/>
+      <c r="F157" s="6">
+        <v>1</v>
+      </c>
+      <c r="G157" s="6"/>
+      <c r="H157" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I157" s="12"/>
+      <c r="J157" s="3"/>
+    </row>
+    <row r="158" spans="1:10" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A158" s="27">
         <v>79</v>
       </c>
-      <c r="B81" s="13">
-        <v>0.63888888888888895</v>
-      </c>
-      <c r="C81" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D81" s="9" t="s">
+      <c r="B158" s="13">
+        <v>0.63890046296296299</v>
+      </c>
+      <c r="C158" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E81" s="5" t="s">
+      <c r="E158" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F158" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="G81" s="6" t="s">
+      <c r="G158" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="H81" s="19" t="s">
+      <c r="H158" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="I81" s="12"/>
-    </row>
-    <row r="82" spans="1:9" ht="120" x14ac:dyDescent="0.2">
-      <c r="A82" s="27">
+      <c r="I158" s="12"/>
+      <c r="J158" s="3"/>
+    </row>
+    <row r="159" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A159" s="27"/>
+      <c r="B159" s="4">
+        <v>0.64513888888888893</v>
+      </c>
+      <c r="C159" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D159" s="9"/>
+      <c r="E159" s="5"/>
+      <c r="F159" s="6">
+        <v>1</v>
+      </c>
+      <c r="G159" s="6"/>
+      <c r="H159" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I159" s="12"/>
+      <c r="J159" s="3"/>
+    </row>
+    <row r="160" spans="1:10" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A160" s="27">
         <v>80</v>
       </c>
-      <c r="B82" s="13">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D82" s="9" t="s">
+      <c r="B160" s="13">
+        <v>0.64584490740740741</v>
+      </c>
+      <c r="C160" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E160" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="F160" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="G160" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="H82" s="19" t="s">
+      <c r="H160" s="19" t="s">
         <v>274</v>
       </c>
-      <c r="I82" s="12"/>
-    </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B195" s="2"/>
-    </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B198" s="3"/>
+      <c r="I160" s="12"/>
+      <c r="J160" s="3"/>
+    </row>
+    <row r="273" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B273" s="2"/>
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B276" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001C4030072D5AFB4E9636EBA78C297410" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="a343ee70e17ae8a6d48de6d8e2e186d8">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0004b569-0a5b-4ed2-9d0a-a219957c0eb6" xmlns:ns3="b99539ed-e5c2-4326-bffc-7da5ea6d9f72" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="44c723bb61cff1f531540bedcbedbc87" ns2:_="" ns3:_="">
+    <xsd:import namespace="0004b569-0a5b-4ed2-9d0a-a219957c0eb6"/>
+    <xsd:import namespace="b99539ed-e5c2-4326-bffc-7da5ea6d9f72"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0004b569-0a5b-4ed2-9d0a-a219957c0eb6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="bd269f43-a109-47fe-82e5-cba44ee82b9d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b99539ed-e5c2-4326-bffc-7da5ea6d9f72" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{44d81303-7264-4f1b-b830-d63ca155df25}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="b99539ed-e5c2-4326-bffc-7da5ea6d9f72">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0004b569-0a5b-4ed2-9d0a-a219957c0eb6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b99539ed-e5c2-4326-bffc-7da5ea6d9f72" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A99AFE2-DBCD-41F0-A80A-C026A61B906B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A380A7C7-91CB-407D-A87D-05EDAE5B4F97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0004b569-0a5b-4ed2-9d0a-a219957c0eb6"/>
+    <ds:schemaRef ds:uri="b99539ed-e5c2-4326-bffc-7da5ea6d9f72"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CE39F22-47F0-42A1-83C0-357201123E31}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0004b569-0a5b-4ed2-9d0a-a219957c0eb6"/>
+    <ds:schemaRef ds:uri="b99539ed-e5c2-4326-bffc-7da5ea6d9f72"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>